--- a/Assets/StreamingAssets/Chapter/Void000.xlsx
+++ b/Assets/StreamingAssets/Chapter/Void000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CEFB58-E802-4A85-BB8E-5C18FCC83745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434BBE6B-080A-440D-B701-46ABC6C47DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="3120" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -38,896 +38,884 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="228">
   <si>
+    <t>Black</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑场</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/脚步声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 0.4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>%Admin%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/对讲机噪声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warning</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/错误噪声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/对讲机噪声|音效/登录成功1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+  </si>
+  <si>
+    <t>虚空_回忆年数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10万年 &gt;&gt; 虚空_回忆年数|100万年 &gt;&gt; 虚空_回忆年数|1000万年 &gt;&gt; 虚空_回忆年数|1亿年 &gt;&gt; 虚空_回忆年数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 那应该有……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>空第一次对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单点 &gt;&gt; ? &gt;&gt; KONG &gt;&gt; 空第一次对话 &gt;&gt; 325 &gt;&gt; 0 &gt;&gt; 0.8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好 &gt;&gt; 21</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不好</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">         &lt;size=20&gt;「虚空意识」&lt;/size&gt;&lt;br&gt;滚开，摄像头&lt;size=20&gt;&lt;br&gt;&lt;color=#FFFFFF00&gt;占位符</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>？ &gt;&gt; 26|…… &gt;&gt; 26</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(有意思)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(让我想想，一个人冒着被同化或者杀死的风险来到世界的底层)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>noti &gt;&gt; 而我，也差不多成为虚空的一部分了 &gt;&gt; KONG &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(那它的身后有更重要的东西吧？)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(可是啊，宏观是很难改变微观的)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(你说是吧，空？)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(你是很难找到那本「书」的，至少对我们而言这些东西是书——况且你要在100年内找到属于自己世界的书，时间够吗？)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(得了，你就自己先大海捞针吧，让我观测观测最近发生了什么……)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//欧亚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//铺地鸹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>欧亚</t>
+  </si>
+  <si>
+    <t>在以钛维海中的一块影生大陆爆发了战事……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>里面，16国争霸，其中有4个大国，一个国度是兽人的国度，另外3个是纯人类的国度。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啧，白虚空？只不过是喜欢在缝中跑来跑去，结果被困住。这愚蠢的意识还被奉为神——脑残。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽人国有着他人都渴望的神——白虚空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>即便他国都极力打压兽人国，但是还是没有办法让兽人国王灭。反而，兽人国靠着白虚空的力量逐步确立了统治地位。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>各国为了求生，建立起“统一战线”。此时，得到白虚空已经不是这么重要了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少不是现在……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类总是这样，总喜欢玩一点狼人杀——哦对，兽人国里面的底层也过得不怎么好吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>为什么呢？滚的人是你吧。如果我想的话——我可以立马把你丢进「回收站」</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>读书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//弗拉赫斯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>从前有个弗拉赫斯人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弗拉赫斯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单点 &gt;&gt; ! &gt;&gt; 前进 &gt;&gt; 前1 &gt;&gt; -325 &gt;&gt; 0 &gt;&gt; 0.8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铺地鸹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一块全是鸟类的大陆，由虚空创生，附着在某个星球上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>然而，其中有一只鸟知道了自己世界必然会湮灭的结局，但他已经老矣——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还可以干一些什么呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是望着天空等待着一个世界之外的人来帮他拯救这个地方吧——顺便压上整个星球。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啧啧啧，很像你——空。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>运气不错，阅读到了另一个和你世界频率一致的世界。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为家住在海边，他喜欢的人在海的另一边。他没有船，只有个勺子，所以他决定用勺子把海水移走。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>开工一天就被海浪卷走淹死了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>和空第二次对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他的世界必然是无救的——我可以帮他，亦然可以结束他的痛苦。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>差不多了，再去看看他。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>何事？还想缠着我？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我给你两个选择：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 放弃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 我帮你</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我凭什么信得过你？虚空？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你想找《EARTH-瑞州》及其子属和主族吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于你来说你这样的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于（除虚空环境）物质守恒，这块地方会被无情地回收……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们做的，首先就是要保证虚空的稳定。就你知道的，虚空的物质不守恒，祂可以凭空创生物质。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不限制你们，我们就会亏损，我们——世界的根基死了，你们呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那你为什么要帮我？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>故我好奇——虚空集合定下的死规则被逾越了会发生什么……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能有这样的书，但是我没有看过——但比起看书，我更想亲眼见证。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>而你帮我，不会被虚空集合排斥吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不会，你也不会。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哼，我还以为你不知道呢？赌狗。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>再见。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以通过微观影响全局是我和你的本事。再者——会有其他替罪羊的，不过替罪羊可以指向你们自己，但是基本上概率为0。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//不管他了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管他了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行啊，你开兴就好……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>再见</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关闭游戏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//管他</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>管他</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抉择1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>backTo &gt;&gt; 抉择1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>敬酒不吃吃罚酒 &gt;&gt; 不管他了|&lt;b&gt;&lt;color=#B5A642&gt;但是我想看到一个完整的故事 &gt;&gt; 管他</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 0.4|backTo &gt;&gt; 抉择1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/拿放东西1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿到了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的书。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>眼睛里这么多疑虑干什么？这可以表示我的诚意了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>*空把书翻到最后一页，上面赫然写了一句话：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>撕了吧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>*空尝试把这一页撕掉，但发现纸张没有办法被损坏……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//给予权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//不给予权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不给予权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>backTo &gt;&gt; 权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>给予权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复如初</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/撕纸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>撕掉结尾是没有用的，我们只可以去影响微观的事物。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(嗯……)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你这本书就先撕这个地方好了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重生</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>取名为空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//新名字_空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>笑话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新的意义</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>//新名字_其他</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他名字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;color=#B5A642&gt;空 &gt;&gt; 取名为空|其他 &gt;&gt; 其他名字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>a149</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>起名字_返回</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>othername</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag &gt;&gt; 空的新名字 == 空 &gt;&gt; 取名为空 &gt;&gt; othername</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;你好！&lt;b&gt;%Admin_UserDomainName% &lt;/b&gt;！</t>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;size=64&gt;&lt;b&gt;fOrEAcH -&gt; &lt;br&gt;booK { I.obJEct.add(read(it &lt;- Kong.dll)) }&lt;br&gt;&lt;size=12&gt;□□001001011111□□□□001010001010101010101111□□□000011101100011□□□□□□□111110011010□□□□□&lt;br&gt;&lt;size=18&gt;Input=&gt;Done</t>
+  </si>
+  <si>
+    <t>removeValueTag &gt;&gt; Kong.dll获取管理员权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*许久未来到此处……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*嗯哼？罕见……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*记不清楚了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*一个声音徘徊在走廊尽头，不知是谁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*或许就是那个不速之客呢？——如果按经验来说的话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*不如去看看</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*返回原处，空坐到了凳子上休息。应该是找书找累了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*凳子……它的用处就是给不想当摄像头的意识用的吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*帮了你这一些忙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*我可以给你——起一个新的名字吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*&lt;b&gt;&lt;color=#B5A642&gt;我有一个「控制不住」的请求</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*你是他1/4的灵魂，机械的完成使命，而你不应该是机械。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*你叫空，一个新的空，你是你自己……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*……，我可以把他当成笑话吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*可以</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;**他坐在地上，显得有些许疲惫。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;**靠近他，他似乎认出我了。他拍了拍身子，站起来，说：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;*&lt;size=64&gt;&lt;b&gt;fOrEAcH -&gt; &lt;br&gt;booKs { Input(booKs.filter("EARTH_000")) }&lt;br&gt;&lt;size=12&gt;□□001001010110110111111□□101010011110110111101001101101111110011010□□□□□&lt;br&gt;&lt;size=18&gt;Input=&gt;new Local(465e - 15.2,275e + 14,17.2e + 0.254)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;我已经，有多少年没见到外来者了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>值信息框 &gt;&gt; Kong.dll获取管理员权限 &gt;&gt; 在给予Kong.dll管理员权限后，你的计算机可能受到威胁，请谨慎处理！ &gt;&gt; 给予此程序管理员权限： &gt;&gt; 同意 &gt;&gt; 拒绝</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag &gt;&gt; Kong.dll获取管理员权限 == True &gt;&gt; 给予权限 &gt;&gt; 不给予权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feature/空 &gt;&gt; 淡入</t>
+  </si>
+  <si>
+    <t>Feature/空 &gt;&gt; 淡出</t>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*&lt;size=64&gt;&lt;b&gt;地球难逃湮灭&lt;br&gt;&lt;size=32&gt;无一生还</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你知道为什么你把那个地方的几页附在一本书上会导致整个地球的湮灭吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>它不是废纸！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空图书馆/虚空图书馆</t>
+  </si>
+  <si>
+    <t>虚空图书馆/读书馆_中</t>
+  </si>
+  <si>
+    <t>虚空图书馆/书架</t>
+  </si>
+  <si>
+    <t>单点 &gt;&gt; ! &gt;&gt; 欧亚 &gt;&gt; 欧亚 &gt;&gt; -355 &gt;&gt; 70 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完欧亚 !has|单点 &gt;&gt; ! &gt;&gt; 弗拉赫斯 &gt;&gt; 弗拉赫斯 &gt;&gt; 330 &gt;&gt; -70 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完弗拉赫斯 !has|单点 &gt;&gt; ! &gt;&gt; 铺地鸹 &gt;&gt; 铺地鸹 &gt;&gt; 120 &gt;&gt; -180 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完铺地鸹 !has|单点 &gt;&gt; &gt; &gt;&gt; 空 &gt;&gt; 和空第二次对话 &gt;&gt; 575 &gt;&gt; 0 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完欧亚 has and 虚空图书馆:读完弗拉赫斯 has and 虚空图书馆:读完铺地鸹 has</t>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 虚空图书馆:读完欧亚|goto &gt;&gt; 读书</t>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 虚空图书馆:读完弗拉赫斯|goto &gt;&gt; 读书</t>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 虚空图书馆:读完铺地鸹|goto &gt;&gt; 读书</t>
+  </si>
+  <si>
+    <t>虚空图书馆/读书馆_后</t>
+  </si>
+  <si>
+    <t>虚空图书馆/虚空图书馆_书</t>
+  </si>
+  <si>
+    <t>addValueTag &gt;&gt; 空的新名字 &gt;&gt; 空|goto &gt;&gt; 重生</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>addValueTag &gt;&gt; 空的新名字 &gt;&gt; 空?|goto &gt;&gt; 重生</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;Scene</t>
+  </si>
+  <si>
+    <t>&amp;VO</t>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;系统终端登录中……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空图书馆/虚空图书馆-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空图书馆/虚空图书馆-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未识别</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;不是这本……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空图书馆/虚空图书馆</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;这也不是……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;我到底还要找多久......?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;color=#FF0000&gt;系统检测到一个可疑的DLL注入行为，目标为kong.dll。通过分析网络流量和系统日志，发现以下异常活动：&lt;br&gt;kong.dll 开始频繁访问网络端口 ?，并尝试与外部IP地址 ? 建立连接。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 1|noti &gt;&gt; 追上可疑的进程 &gt;&gt; Defender &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(它走了？)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>noti &gt;&gt; 了解完底细，该去找他了 &gt;&gt; %Admin% &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(可是……为什么？)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 1|saveN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/纸质书翻页</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>差点忘了——你权限不够。就你的后门也获取不了多大的权限。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想……我不能给予你这个权限，但是，我会替你做我允许的事情。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>撕书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>gotoN &gt;&gt; 撕书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想……给不给你权限都一样，但是为了省事，或是保证你一定的安全，给你权限还是有必要的——再试试？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到书上的连线了吗？时间线由无数个微观的因和果推进，所以，我们无法影响宏观。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;你打算叫我什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就是笑话 &gt;&gt; 笑话|这是你新的意义 &gt;&gt; 新的意义|换个名字 &gt;&gt; 起名字_返回</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;你叫%tag &gt;&gt; 空的新名字%，不再被自我束缚。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;*但一切看你，不过这是你新的意义</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto &gt;&gt; 重生|backTo &gt;&gt; 其他名字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入 &gt;&gt; 空的新名字 &gt;&gt; 你叫&lt;br&gt;&lt;size=18&gt;%Admin%，为了系统安全，请勿不输入字符！ &gt;&gt; a149 &gt;&gt; 起名字_返回</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeTags &gt;&gt; 虚空图书馆:读完欧亚 虚空图书馆:读完弗拉赫斯 虚空图书馆:读完铺地鸹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/SCP-x6x</t>
+  </si>
+  <si>
+    <t>音乐/SCP-x6x|音效/错误噪声</t>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;color=#FF0000&gt;&lt;b&gt;定&lt;b&gt;&lt;i&gt;位&lt;size=□&gt;&lt;size=32&gt;到&lt;size=18&gt;欲&lt;/size&gt;?F非&lt;/f&gt;法植入的{zh_cn:程序|en: prog□e}——KoN_□G.ex□</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真正引发那场灾难的是你所知的高维文明——毕竟你已经带着祂们的制作的武器复仇了，不是吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于我们的图书馆，它也是有空间限制的。有东西被毁灭是一个既定事件，而它刚好是瑞州，瑞州就成了废纸。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>然而你们的宇宙的物质是守恒的——然而正是虚空创生的物质得以让海或者宇宙守恒。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为什纳指向的是那个地方，地球融合它后，什纳将目标指针指向了地球。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看过很多本关于试图抵抗既定结果的故事，无一是成功的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OverTheChapter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>人物</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>对话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>语音</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>背景/cg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>背景音乐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>转场特效</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘层</t>
+  </si>
+  <si>
+    <t>对话框头像</t>
+  </si>
+  <si>
+    <t>#TAG</t>
   </si>
   <si>
     <t>选项</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
   </si>
   <si>
     <t>指令</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#TAG</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑场</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/脚步声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 0.4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>%Admin%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/对讲机噪声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Warning</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/错误噪声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait &gt;&gt; 5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/对讲机噪声|音效/登录成功1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>……</t>
-  </si>
-  <si>
-    <t>虚空_回忆年数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10万年 &gt;&gt; 虚空_回忆年数|100万年 &gt;&gt; 虚空_回忆年数|1000万年 &gt;&gt; 虚空_回忆年数|1亿年 &gt;&gt; 虚空_回忆年数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>前1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 那应该有……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>空第一次对话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>单点 &gt;&gt; ? &gt;&gt; KONG &gt;&gt; 空第一次对话 &gt;&gt; 325 &gt;&gt; 0 &gt;&gt; 0.8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好 &gt;&gt; 21</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我不好</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">         &lt;size=20&gt;「虚空意识」&lt;/size&gt;&lt;br&gt;滚开，摄像头&lt;size=20&gt;&lt;br&gt;&lt;color=#FFFFFF00&gt;占位符</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>？ &gt;&gt; 26|…… &gt;&gt; 26</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(有意思)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(让我想想，一个人冒着被同化或者杀死的风险来到世界的底层)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>noti &gt;&gt; 而我，也差不多成为虚空的一部分了 &gt;&gt; KONG &gt;&gt; 3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(那它的身后有更重要的东西吧？)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(可是啊，宏观是很难改变微观的)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(你说是吧，空？)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(你是很难找到那本「书」的，至少对我们而言这些东西是书——况且你要在100年内找到属于自己世界的书，时间够吗？)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(得了，你就自己先大海捞针吧，让我观测观测最近发生了什么……)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//欧亚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//铺地鸹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>欧亚</t>
-  </si>
-  <si>
-    <t>在以钛维海中的一块影生大陆爆发了战事……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>里面，16国争霸，其中有4个大国，一个国度是兽人的国度，另外3个是纯人类的国度。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啧，白虚空？只不过是喜欢在缝中跑来跑去，结果被困住。这愚蠢的意识还被奉为神——脑残。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>兽人国有着他人都渴望的神——白虚空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>即便他国都极力打压兽人国，但是还是没有办法让兽人国王灭。反而，兽人国靠着白虚空的力量逐步确立了统治地位。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>各国为了求生，建立起“统一战线”。此时，得到白虚空已经不是这么重要了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>至少不是现在……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类总是这样，总喜欢玩一点狼人杀——哦对，兽人国里面的底层也过得不怎么好吧？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>为什么呢？滚的人是你吧。如果我想的话——我可以立马把你丢进「回收站」</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>读书</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//弗拉赫斯</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>从前有个弗拉赫斯人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>弗拉赫斯</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>单点 &gt;&gt; ! &gt;&gt; 前进 &gt;&gt; 前1 &gt;&gt; -325 &gt;&gt; 0 &gt;&gt; 0.8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>铺地鸹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一块全是鸟类的大陆，由虚空创生，附着在某个星球上。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>然而，其中有一只鸟知道了自己世界必然会湮灭的结局，但他已经老矣——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还可以干一些什么呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>只是望着天空等待着一个世界之外的人来帮他拯救这个地方吧——顺便压上整个星球。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啧啧啧，很像你——空。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>运气不错，阅读到了另一个和你世界频率一致的世界。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>因为家住在海边，他喜欢的人在海的另一边。他没有船，只有个勺子，所以他决定用勺子把海水移走。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>开工一天就被海浪卷走淹死了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>和空第二次对话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他的世界必然是无救的——我可以帮他，亦然可以结束他的痛苦。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>差不多了，再去看看他。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>何事？还想缠着我？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我给你两个选择：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 放弃</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 我帮你</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我凭什么信得过你？虚空？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你想找《EARTH-瑞州》及其子属和主族吧？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对于你来说你这样的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>由于（除虚空环境）物质守恒，这块地方会被无情地回收……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我们做的，首先就是要保证虚空的稳定。就你知道的，虚空的物质不守恒，祂可以凭空创生物质。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不限制你们，我们就会亏损，我们——世界的根基死了，你们呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那你为什么要帮我？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>故我好奇——虚空集合定下的死规则被逾越了会发生什么……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可能有这样的书，但是我没有看过——但比起看书，我更想亲眼见证。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>而你帮我，不会被虚空集合排斥吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不会，你也不会。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哼，我还以为你不知道呢？赌狗。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>再见。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以通过微观影响全局是我和你的本事。再者——会有其他替罪羊的，不过替罪羊可以指向你们自己，但是基本上概率为0。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//不管他了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管他了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>行啊，你开兴就好……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>再见</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>关闭游戏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//管他</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>管他</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait &gt;&gt; 3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>抉择1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>backTo &gt;&gt; 抉择1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>敬酒不吃吃罚酒 &gt;&gt; 不管他了|&lt;b&gt;&lt;color=#B5A642&gt;但是我想看到一个完整的故事 &gt;&gt; 管他</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 0.4|backTo &gt;&gt; 抉择1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/拿放东西1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>拿到了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的书。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>眼睛里这么多疑虑干什么？这可以表示我的诚意了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>*空把书翻到最后一页，上面赫然写了一句话：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>撕了吧</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>*空尝试把这一页撕掉，但发现纸张没有办法被损坏……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//给予权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//不给予权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不给予权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>backTo &gt;&gt; 权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>给予权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复如初</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/撕纸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>撕掉结尾是没有用的，我们只可以去影响微观的事物。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(嗯……)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你这本书就先撕这个地方好了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>重生</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>取名为空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//新名字_空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>笑话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>新的意义</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>//新名字_其他</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他名字</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;color=#B5A642&gt;空 &gt;&gt; 取名为空|其他 &gt;&gt; 其他名字</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>a149</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>起名字_返回</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>othername</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag &gt;&gt; 空的新名字 == 空 &gt;&gt; 取名为空 &gt;&gt; othername</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;你好！&lt;b&gt;%Admin_UserDomainName% &lt;/b&gt;！</t>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;size=64&gt;&lt;b&gt;fOrEAcH -&gt; &lt;br&gt;booK { I.obJEct.add(read(it &lt;- Kong.dll)) }&lt;br&gt;&lt;size=12&gt;□□001001011111□□□□001010001010101010101111□□□000011101100011□□□□□□□111110011010□□□□□&lt;br&gt;&lt;size=18&gt;Input=&gt;Done</t>
-  </si>
-  <si>
-    <t>removeValueTag &gt;&gt; Kong.dll获取管理员权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*许久未来到此处……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*嗯哼？罕见……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*记不清楚了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*一个声音徘徊在走廊尽头，不知是谁</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*或许就是那个不速之客呢？——如果按经验来说的话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*不如去看看</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*返回原处，空坐到了凳子上休息。应该是找书找累了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*凳子……它的用处就是给不想当摄像头的意识用的吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*帮了你这一些忙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*我可以给你——起一个新的名字吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*&lt;b&gt;&lt;color=#B5A642&gt;我有一个「控制不住」的请求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*你是他1/4的灵魂，机械的完成使命，而你不应该是机械。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*你叫空，一个新的空，你是你自己……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*……，我可以把他当成笑话吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*可以</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;**他坐在地上，显得有些许疲惫。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;**靠近他，他似乎认出我了。他拍了拍身子，站起来，说：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;*&lt;size=64&gt;&lt;b&gt;fOrEAcH -&gt; &lt;br&gt;booKs { Input(booKs.filter("EARTH_000")) }&lt;br&gt;&lt;size=12&gt;□□001001010110110111111□□101010011110110111101001101101111110011010□□□□□&lt;br&gt;&lt;size=18&gt;Input=&gt;new Local(465e - 15.2,275e + 14,17.2e + 0.254)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;我已经，有多少年没见到外来者了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>值信息框 &gt;&gt; Kong.dll获取管理员权限 &gt;&gt; 在给予Kong.dll管理员权限后，你的计算机可能受到威胁，请谨慎处理！ &gt;&gt; 给予此程序管理员权限： &gt;&gt; 同意 &gt;&gt; 拒绝</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag &gt;&gt; Kong.dll获取管理员权限 == True &gt;&gt; 给予权限 &gt;&gt; 不给予权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框头像</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Feature/空 &gt;&gt; 淡入</t>
-  </si>
-  <si>
-    <t>Feature/空 &gt;&gt; 淡出</t>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*&lt;size=64&gt;&lt;b&gt;地球难逃湮灭&lt;br&gt;&lt;size=32&gt;无一生还</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你知道为什么你把那个地方的几页附在一本书上会导致整个地球的湮灭吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>它不是废纸！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚空图书馆/虚空图书馆</t>
-  </si>
-  <si>
-    <t>虚空图书馆/读书馆_中</t>
-  </si>
-  <si>
-    <t>虚空图书馆/书架</t>
-  </si>
-  <si>
-    <t>单点 &gt;&gt; ! &gt;&gt; 欧亚 &gt;&gt; 欧亚 &gt;&gt; -355 &gt;&gt; 70 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完欧亚 !has|单点 &gt;&gt; ! &gt;&gt; 弗拉赫斯 &gt;&gt; 弗拉赫斯 &gt;&gt; 330 &gt;&gt; -70 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完弗拉赫斯 !has|单点 &gt;&gt; ! &gt;&gt; 铺地鸹 &gt;&gt; 铺地鸹 &gt;&gt; 120 &gt;&gt; -180 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完铺地鸹 !has|单点 &gt;&gt; &gt; &gt;&gt; 空 &gt;&gt; 和空第二次对话 &gt;&gt; 575 &gt;&gt; 0 &gt;&gt; 1 &lt;&lt; 虚空图书馆:读完欧亚 has and 虚空图书馆:读完弗拉赫斯 has and 虚空图书馆:读完铺地鸹 has</t>
-  </si>
-  <si>
-    <t>addTag &gt;&gt; 虚空图书馆:读完欧亚|goto &gt;&gt; 读书</t>
-  </si>
-  <si>
-    <t>addTag &gt;&gt; 虚空图书馆:读完弗拉赫斯|goto &gt;&gt; 读书</t>
-  </si>
-  <si>
-    <t>addTag &gt;&gt; 虚空图书馆:读完铺地鸹|goto &gt;&gt; 读书</t>
-  </si>
-  <si>
-    <t>虚空图书馆/读书馆_后</t>
-  </si>
-  <si>
-    <t>虚空图书馆/虚空图书馆_书</t>
-  </si>
-  <si>
-    <t>addValueTag &gt;&gt; 空的新名字 &gt;&gt; 空|goto &gt;&gt; 重生</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>addValueTag &gt;&gt; 空的新名字 &gt;&gt; 空?|goto &gt;&gt; 重生</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;Scene</t>
-  </si>
-  <si>
-    <t>&amp;VO</t>
-  </si>
-  <si>
-    <t>R</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;系统终端登录中……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;淡入&gt;&lt;中心文本&gt;……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚空图书馆/虚空图书馆-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚空图书馆/虚空图书馆-2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>未识别</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;不是这本……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚空图书馆/虚空图书馆</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;这也不是……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;我到底还要找多久......?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;color=#FF0000&gt;系统检测到一个可疑的DLL注入行为，目标为kong.dll。通过分析网络流量和系统日志，发现以下异常活动：&lt;br&gt;kong.dll 开始频繁访问网络端口 ?，并尝试与外部IP地址 ? 建立连接。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 1|noti &gt;&gt; 追上可疑的进程 &gt;&gt; Defender &gt;&gt; 3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(它走了？)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>noti &gt;&gt; 了解完底细，该去找他了 &gt;&gt; %Admin% &gt;&gt; 3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(可是……为什么？)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 1|saveN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/纸质书翻页</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>差点忘了——你权限不够。就你的后门也获取不了多大的权限。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我想……我不能给予你这个权限，但是，我会替你做我允许的事情。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>撕书</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>gotoN &gt;&gt; 撕书</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我想……给不给你权限都一样，但是为了省事，或是保证你一定的安全，给你权限还是有必要的——再试试？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看到书上的连线了吗？时间线由无数个微观的因和果推进，所以，我们无法影响宏观。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;你打算叫我什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这就是笑话 &gt;&gt; 笑话|这是你新的意义 &gt;&gt; 新的意义|换个名字 &gt;&gt; 起名字_返回</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;你叫%tag &gt;&gt; 空的新名字%，不再被自我束缚。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;*但一切看你，不过这是你新的意义</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goto &gt;&gt; 重生|backTo &gt;&gt; 其他名字</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>输入 &gt;&gt; 空的新名字 &gt;&gt; 你叫&lt;br&gt;&lt;size=18&gt;%Admin%，为了系统安全，请勿不输入字符！ &gt;&gt; a149 &gt;&gt; 起名字_返回</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeTags &gt;&gt; 虚空图书馆:读完欧亚 虚空图书馆:读完弗拉赫斯 虚空图书馆:读完铺地鸹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/SCP-x6x</t>
-  </si>
-  <si>
-    <t>音乐/SCP-x6x|音效/错误噪声</t>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;color=#FF0000&gt;&lt;b&gt;定&lt;b&gt;&lt;i&gt;位&lt;size=□&gt;&lt;size=32&gt;到&lt;size=18&gt;欲&lt;/size&gt;?F非&lt;/f&gt;法植入的{zh_cn:程序|en: prog□e}——KoN_□G.ex□</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>真正引发那场灾难的是你所知的高维文明——毕竟你已经带着祂们的制作的武器复仇了，不是吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对于我们的图书馆，它也是有空间限制的。有东西被毁灭是一个既定事件，而它刚好是瑞州，瑞州就成了废纸。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>然而你们的宇宙的物质是守恒的——然而正是虚空创生的物质得以让海或者宇宙守恒。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>因为什纳指向的是那个地方，地球融合它后，什纳将目标指针指向了地球。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我看过很多本关于试图抵抗既定结果的故事，无一是成功的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OverTheChapter</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1327,364 +1315,364 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>8</v>
+        <v>225</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>7</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I12" s="6"/>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I13" s="6"/>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I14" s="6"/>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>23</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L22" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I27" s="6">
         <v>21</v>
@@ -1692,61 +1680,61 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="I30" s="6"/>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I32" s="6">
         <v>26</v>
@@ -1754,198 +1742,198 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I37" s="6"/>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L38" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I39" s="6"/>
       <c r="L39" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L41" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="I42" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K42" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L53" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I56" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I58" s="6"/>
       <c r="L58" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -1953,414 +1941,414 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I67" s="6"/>
       <c r="L67" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L69" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I71" s="6"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G73" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D74" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G74" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I75" s="6"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I80" s="6"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="I81" s="6"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I84" s="6"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="I86" s="6"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" t="s">
         <v>78</v>
-      </c>
-      <c r="B89" t="s">
-        <v>89</v>
       </c>
       <c r="I89" s="6"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I92" s="6"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G101" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="J102" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="L102" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
@@ -2368,580 +2356,580 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="L105" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I107" s="6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L107" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L109" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F110" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I110" s="6"/>
       <c r="L110" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F113" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I114" s="6"/>
       <c r="L114" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G115" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I115" s="6"/>
       <c r="L115" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G119" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B120" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C120" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D120" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F120" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G120" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I120" s="6"/>
       <c r="L120" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I121" s="6"/>
       <c r="L121" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B125" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L126" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I127" s="6"/>
       <c r="L127" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L130" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I131" s="6"/>
       <c r="L131" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D133" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B134" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C134" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B135" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F135" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I135" s="6"/>
       <c r="L135" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="I137" s="6"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B140" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C140" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I147" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J147" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="I149" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="J150" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I151" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="L151" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="I152" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="L152" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B154" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I154" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L154" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="I155" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B157" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="I157" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L157" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B159" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D159" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G159" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H159" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I159" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L160" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Void000.xlsx
+++ b/Assets/StreamingAssets/Chapter/Void000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434BBE6B-080A-440D-B701-46ABC6C47DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CEFB58-E802-4A85-BB8E-5C18FCC83745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="3120" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,50 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="228">
   <si>
+    <t>人物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景/cg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>转场特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#TAG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Black</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -658,6 +702,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>对话框头像</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Feature/空 &gt;&gt; 淡入</t>
   </si>
   <si>
@@ -721,6 +769,10 @@
     <t>&amp;VO</t>
   </si>
   <si>
+    <t>R</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>&lt;中心文本&gt;系统终端登录中……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -876,46 +928,6 @@
   </si>
   <si>
     <t>OverTheChapter</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人物</t>
-  </si>
-  <si>
-    <t>对话</t>
-  </si>
-  <si>
-    <t>语音</t>
-  </si>
-  <si>
-    <t>背景/cg</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>转场特效</t>
-  </si>
-  <si>
-    <t>立绘层</t>
-  </si>
-  <si>
-    <t>对话框头像</t>
-  </si>
-  <si>
-    <t>#TAG</t>
-  </si>
-  <si>
-    <t>选项</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
-  </si>
-  <si>
-    <t>指令</t>
-  </si>
-  <si>
-    <t>Feature/空 &gt;&gt; 淡入</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1315,364 +1327,364 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>217</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>218</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>221</v>
+        <v>9</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>225</v>
+        <v>8</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3</v>
       </c>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F12" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I12" s="6"/>
       <c r="L12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I13" s="6"/>
       <c r="L13" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I14" s="6"/>
       <c r="L14" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="L22" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F25" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I27" s="6">
         <v>21</v>
@@ -1680,61 +1692,61 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I30" s="6"/>
       <c r="L30" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I32" s="6">
         <v>26</v>
@@ -1742,198 +1754,198 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I37" s="6"/>
       <c r="L37" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L38" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="I39" s="6"/>
       <c r="L39" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L41" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I42" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K42" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L53" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I58" s="6"/>
       <c r="L58" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -1941,414 +1953,414 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="I66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="I67" s="6"/>
       <c r="L67" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L69" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F71" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I71" s="6"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F74" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I75" s="6"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I80" s="6"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="I81" s="6"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I84" s="6"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I86" s="6"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I89" s="6"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I92" s="6"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B98" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B100" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J102" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L102" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
@@ -2356,580 +2368,580 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="L105" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I107" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L107" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L109" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I110" s="6"/>
       <c r="L110" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D113" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F113" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I114" s="6"/>
       <c r="L114" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C115" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G115" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I115" s="6"/>
       <c r="L115" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B116" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G116" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B117" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B119" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D119" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G119" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B120" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C120" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F120" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I120" s="6"/>
       <c r="L120" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B121" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I121" s="6"/>
       <c r="L121" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B122" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B123" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B125" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B126" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="L126" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B127" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I127" s="6"/>
       <c r="L127" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B130" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L130" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I131" s="6"/>
       <c r="L131" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B133" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D133" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C134" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D134" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F134" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D135" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F135" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I135" s="6"/>
       <c r="L135" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B136" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="I137" s="6"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B139" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D139" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B140" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C140" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D140" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F140" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="I147" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="J147" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I149" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J150" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I151" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="L151" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I152" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L152" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I154" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L154" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I155" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B157" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="I157" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L157" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D159" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G159" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H159" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I159" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L160" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
